--- a/artfynd/A 62197-2025 artfynd.xlsx
+++ b/artfynd/A 62197-2025 artfynd.xlsx
@@ -1055,7 +1055,7 @@
         <v>131106322</v>
       </c>
       <c r="B5" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>131106324</v>
       </c>
       <c r="B6" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>131106316</v>
       </c>
       <c r="B7" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>131106309</v>
       </c>
       <c r="B8" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>131106326</v>
       </c>
       <c r="B9" t="n">
-        <v>92184</v>
+        <v>92185</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>131106319</v>
       </c>
       <c r="B10" t="n">
-        <v>92111</v>
+        <v>92112</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>131106315</v>
       </c>
       <c r="B11" t="n">
-        <v>92111</v>
+        <v>92112</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>131106321</v>
       </c>
       <c r="B12" t="n">
-        <v>92026</v>
+        <v>92027</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2013,10 +2013,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131106314</v>
+        <v>131106312</v>
       </c>
       <c r="B13" t="n">
-        <v>91813</v>
+        <v>92112</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2024,28 +2024,24 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>mycel</t>
@@ -2057,10 +2053,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601556</v>
+        <v>601540</v>
       </c>
       <c r="R13" t="n">
-        <v>6992605</v>
+        <v>6992576</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2087,7 +2083,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2025_0870</t>
+          <t>2025_0872</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2097,7 +2093,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2107,7 +2103,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2127,7 +2123,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2138,10 +2134,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131106312</v>
+        <v>131106325</v>
       </c>
       <c r="B14" t="n">
-        <v>92111</v>
+        <v>91814</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,21 +2145,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2178,10 +2174,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601540</v>
+        <v>601615</v>
       </c>
       <c r="R14" t="n">
-        <v>6992576</v>
+        <v>6992785</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2208,7 +2204,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2025_0872</t>
+          <t>2025_0858</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2218,7 +2214,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2228,7 +2224,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2259,10 +2255,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131106325</v>
+        <v>131106314</v>
       </c>
       <c r="B15" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2287,7 +2283,11 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>mycel</t>
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>601615</v>
+        <v>601556</v>
       </c>
       <c r="R15" t="n">
-        <v>6992785</v>
+        <v>6992605</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2025_0858</t>
+          <t>2025_0870</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2380,10 +2380,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131106320</v>
+        <v>131106308</v>
       </c>
       <c r="B16" t="n">
-        <v>58043</v>
+        <v>91814</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2391,34 +2391,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gunnes gamla tomt, Ång</t>
+          <t>Grunnes gamla tomt, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>601577</v>
+        <v>601505</v>
       </c>
       <c r="R16" t="n">
-        <v>6992687</v>
+        <v>6992571</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2025_0863</t>
+          <t>2025_0876</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Forsberg</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2496,10 +2496,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131106308</v>
+        <v>131106320</v>
       </c>
       <c r="B17" t="n">
-        <v>91813</v>
+        <v>58043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2507,34 +2507,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Grunnes gamla tomt, Ång</t>
+          <t>Gunnes gamla tomt, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>601505</v>
+        <v>601577</v>
       </c>
       <c r="R17" t="n">
-        <v>6992571</v>
+        <v>6992687</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2025_0876</t>
+          <t>2025_0863</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Anders Forsberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2735,7 +2735,7 @@
         <v>131106318</v>
       </c>
       <c r="B19" t="n">
-        <v>92111</v>
+        <v>92112</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2857,10 +2857,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131106310</v>
+        <v>131106313</v>
       </c>
       <c r="B20" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2885,17 +2885,26 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Grunnes gamla tomt, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>601470</v>
+        <v>601530</v>
       </c>
       <c r="R20" t="n">
-        <v>6992568</v>
+        <v>6992589</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2922,7 +2931,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2025_0874</t>
+          <t>2025_0871</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2932,7 +2941,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2942,7 +2951,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2962,7 +2971,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2973,10 +2982,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131106313</v>
+        <v>131106310</v>
       </c>
       <c r="B21" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3001,26 +3010,17 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Grunnes gamla tomt, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>601530</v>
+        <v>601470</v>
       </c>
       <c r="R21" t="n">
-        <v>6992589</v>
+        <v>6992568</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2025_0871</t>
+          <t>2025_0874</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -3101,7 +3101,7 @@
         <v>131106317</v>
       </c>
       <c r="B22" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3214,10 +3214,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131106311</v>
+        <v>131106327</v>
       </c>
       <c r="B23" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3243,16 +3243,21 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Grunnes gamla tomt, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>601498</v>
+        <v>601607</v>
       </c>
       <c r="R23" t="n">
-        <v>6992583</v>
+        <v>6992789</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3279,7 +3284,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2025_0873</t>
+          <t>2025_0856</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -3289,7 +3294,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3299,7 +3304,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3319,7 +3324,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>David Isaksson, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3330,10 +3335,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131106327</v>
+        <v>131106311</v>
       </c>
       <c r="B24" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3359,21 +3364,16 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Grunnes gamla tomt, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>601607</v>
+        <v>601498</v>
       </c>
       <c r="R24" t="n">
-        <v>6992789</v>
+        <v>6992583</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2025_0856</t>
+          <t>2025_0873</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>David Isaksson, Alexander Hoffmann</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3451,10 +3451,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131106323</v>
+        <v>131108353</v>
       </c>
       <c r="B25" t="n">
-        <v>92111</v>
+        <v>10966</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3462,34 +3462,38 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Paykull, 1790)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Grunnes gamla tomt, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>601607</v>
+        <v>601612</v>
       </c>
       <c r="R25" t="n">
-        <v>6992738</v>
+        <v>6992796</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3516,7 +3520,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2025_0860</t>
+          <t>2025_0855</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -3526,7 +3530,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3536,7 +3540,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Granlåga med både rynkskinn, ull-och violticka</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3567,10 +3576,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131108353</v>
+        <v>131106323</v>
       </c>
       <c r="B26" t="n">
-        <v>10966</v>
+        <v>92112</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3578,38 +3587,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>101449</v>
+        <v>658</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Grunnes gamla tomt, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>601612</v>
+        <v>601607</v>
       </c>
       <c r="R26" t="n">
-        <v>6992796</v>
+        <v>6992738</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3636,7 +3641,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2025_0855</t>
+          <t>2025_0860</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3646,7 +3651,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3656,12 +3661,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:09</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Granlåga med både rynkskinn, ull-och violticka</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3695,7 +3695,7 @@
         <v>131106330</v>
       </c>
       <c r="B27" t="n">
-        <v>92111</v>
+        <v>92112</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>131106329</v>
       </c>
       <c r="B28" t="n">
-        <v>92272</v>
+        <v>92273</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 62197-2025 artfynd.xlsx
+++ b/artfynd/A 62197-2025 artfynd.xlsx
@@ -3214,10 +3214,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131106327</v>
+        <v>131106323</v>
       </c>
       <c r="B23" t="n">
-        <v>91814</v>
+        <v>92112</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3225,29 +3225,24 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Grunnes gamla tomt, Ång</t>
@@ -3257,7 +3252,7 @@
         <v>601607</v>
       </c>
       <c r="R23" t="n">
-        <v>6992789</v>
+        <v>6992738</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3284,7 +3279,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2025_0856</t>
+          <t>2025_0860</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -3294,7 +3289,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3304,7 +3299,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3324,7 +3319,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>David Isaksson, Alexander Hoffmann</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3335,7 +3330,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131106311</v>
+        <v>131106327</v>
       </c>
       <c r="B24" t="n">
         <v>91814</v>
@@ -3364,16 +3359,21 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Grunnes gamla tomt, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>601498</v>
+        <v>601607</v>
       </c>
       <c r="R24" t="n">
-        <v>6992583</v>
+        <v>6992789</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2025_0873</t>
+          <t>2025_0856</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>David Isaksson, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3451,10 +3451,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131108353</v>
+        <v>131106311</v>
       </c>
       <c r="B25" t="n">
-        <v>10966</v>
+        <v>91814</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3462,38 +3462,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>101449</v>
+        <v>1202</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Grunnes gamla tomt, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>601612</v>
+        <v>601498</v>
       </c>
       <c r="R25" t="n">
-        <v>6992796</v>
+        <v>6992583</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3520,7 +3516,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2025_0855</t>
+          <t>2025_0873</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -3530,7 +3526,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3540,12 +3536,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:09</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Granlåga med både rynkskinn, ull-och violticka</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3565,7 +3556,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3576,10 +3567,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131106323</v>
+        <v>131108353</v>
       </c>
       <c r="B26" t="n">
-        <v>92112</v>
+        <v>10966</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3587,34 +3578,38 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Paykull, 1790)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Grunnes gamla tomt, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>601607</v>
+        <v>601612</v>
       </c>
       <c r="R26" t="n">
-        <v>6992738</v>
+        <v>6992796</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3641,7 +3636,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2025_0860</t>
+          <t>2025_0855</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3651,7 +3646,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3661,7 +3656,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Granlåga med både rynkskinn, ull-och violticka</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 62197-2025 artfynd.xlsx
+++ b/artfynd/A 62197-2025 artfynd.xlsx
@@ -1055,7 +1055,7 @@
         <v>131106322</v>
       </c>
       <c r="B5" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>131106324</v>
       </c>
       <c r="B6" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>131106316</v>
       </c>
       <c r="B7" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>131106309</v>
       </c>
       <c r="B8" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>131106326</v>
       </c>
       <c r="B9" t="n">
-        <v>92185</v>
+        <v>92187</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>131106319</v>
       </c>
       <c r="B10" t="n">
-        <v>92112</v>
+        <v>92114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>131106315</v>
       </c>
       <c r="B11" t="n">
-        <v>92112</v>
+        <v>92114</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>131106321</v>
       </c>
       <c r="B12" t="n">
-        <v>92027</v>
+        <v>92029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2013,10 +2013,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131106312</v>
+        <v>131106314</v>
       </c>
       <c r="B13" t="n">
-        <v>92112</v>
+        <v>91816</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2024,24 +2024,28 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>mycel</t>
@@ -2053,10 +2057,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601540</v>
+        <v>601556</v>
       </c>
       <c r="R13" t="n">
-        <v>6992576</v>
+        <v>6992605</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2083,7 +2087,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2025_0872</t>
+          <t>2025_0870</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2093,7 +2097,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2103,7 +2107,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2123,7 +2127,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2134,10 +2138,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131106325</v>
+        <v>131106312</v>
       </c>
       <c r="B14" t="n">
-        <v>91814</v>
+        <v>92114</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2145,21 +2149,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2174,10 +2178,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601615</v>
+        <v>601540</v>
       </c>
       <c r="R14" t="n">
-        <v>6992785</v>
+        <v>6992576</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2204,7 +2208,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2025_0858</t>
+          <t>2025_0872</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2214,7 +2218,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2224,7 +2228,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2255,10 +2259,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131106314</v>
+        <v>131106325</v>
       </c>
       <c r="B15" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2283,11 +2287,7 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>mycel</t>
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>601556</v>
+        <v>601615</v>
       </c>
       <c r="R15" t="n">
-        <v>6992605</v>
+        <v>6992785</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2025_0870</t>
+          <t>2025_0858</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2383,7 +2383,7 @@
         <v>131106308</v>
       </c>
       <c r="B16" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>131106320</v>
       </c>
       <c r="B17" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>131106289</v>
       </c>
       <c r="B18" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>131106318</v>
       </c>
       <c r="B19" t="n">
-        <v>92112</v>
+        <v>92114</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2857,10 +2857,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131106313</v>
+        <v>131106310</v>
       </c>
       <c r="B20" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2885,26 +2885,17 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Grunnes gamla tomt, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>601530</v>
+        <v>601470</v>
       </c>
       <c r="R20" t="n">
-        <v>6992589</v>
+        <v>6992568</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2931,7 +2922,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2025_0871</t>
+          <t>2025_0874</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2941,7 +2932,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2951,7 +2942,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2971,7 +2962,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2982,10 +2973,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131106310</v>
+        <v>131106313</v>
       </c>
       <c r="B21" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3010,17 +3001,26 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Grunnes gamla tomt, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>601470</v>
+        <v>601530</v>
       </c>
       <c r="R21" t="n">
-        <v>6992568</v>
+        <v>6992589</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2025_0874</t>
+          <t>2025_0871</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -3101,7 +3101,7 @@
         <v>131106317</v>
       </c>
       <c r="B22" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3214,10 +3214,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131106323</v>
+        <v>131108353</v>
       </c>
       <c r="B23" t="n">
-        <v>92112</v>
+        <v>10966</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3225,34 +3225,38 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Paykull, 1790)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Grunnes gamla tomt, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>601607</v>
+        <v>601612</v>
       </c>
       <c r="R23" t="n">
-        <v>6992738</v>
+        <v>6992796</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3279,7 +3283,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2025_0860</t>
+          <t>2025_0855</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -3289,7 +3293,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3299,7 +3303,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Granlåga med både rynkskinn, ull-och violticka</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3330,10 +3339,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131106327</v>
+        <v>131106311</v>
       </c>
       <c r="B24" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3359,21 +3368,16 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Grunnes gamla tomt, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>601607</v>
+        <v>601498</v>
       </c>
       <c r="R24" t="n">
-        <v>6992789</v>
+        <v>6992583</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3400,7 +3404,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2025_0856</t>
+          <t>2025_0873</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -3410,7 +3414,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3420,7 +3424,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3440,7 +3444,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>David Isaksson, Alexander Hoffmann</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3451,10 +3455,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131106311</v>
+        <v>131106327</v>
       </c>
       <c r="B25" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3480,16 +3484,21 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Grunnes gamla tomt, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>601498</v>
+        <v>601607</v>
       </c>
       <c r="R25" t="n">
-        <v>6992583</v>
+        <v>6992789</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3516,7 +3525,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2025_0873</t>
+          <t>2025_0856</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -3526,7 +3535,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3536,7 +3545,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3556,7 +3565,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>David Isaksson, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3567,10 +3576,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131108353</v>
+        <v>131106323</v>
       </c>
       <c r="B26" t="n">
-        <v>10966</v>
+        <v>92114</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3578,38 +3587,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>101449</v>
+        <v>658</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Grunnes gamla tomt, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>601612</v>
+        <v>601607</v>
       </c>
       <c r="R26" t="n">
-        <v>6992796</v>
+        <v>6992738</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3636,7 +3641,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2025_0855</t>
+          <t>2025_0860</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3646,7 +3651,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3656,12 +3661,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:09</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Granlåga med både rynkskinn, ull-och violticka</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3695,7 +3695,7 @@
         <v>131106330</v>
       </c>
       <c r="B27" t="n">
-        <v>92112</v>
+        <v>92114</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>131106329</v>
       </c>
       <c r="B28" t="n">
-        <v>92273</v>
+        <v>92275</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 62197-2025 artfynd.xlsx
+++ b/artfynd/A 62197-2025 artfynd.xlsx
@@ -1055,7 +1055,7 @@
         <v>131106322</v>
       </c>
       <c r="B5" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>131106324</v>
       </c>
       <c r="B6" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>131106316</v>
       </c>
       <c r="B7" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>131106309</v>
       </c>
       <c r="B8" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>131106326</v>
       </c>
       <c r="B9" t="n">
-        <v>92187</v>
+        <v>92188</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>131106319</v>
       </c>
       <c r="B10" t="n">
-        <v>92114</v>
+        <v>92115</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>131106315</v>
       </c>
       <c r="B11" t="n">
-        <v>92114</v>
+        <v>92115</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>131106321</v>
       </c>
       <c r="B12" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>131106314</v>
       </c>
       <c r="B13" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>131106312</v>
       </c>
       <c r="B14" t="n">
-        <v>92114</v>
+        <v>92115</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>131106325</v>
       </c>
       <c r="B15" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>131106308</v>
       </c>
       <c r="B16" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>131106320</v>
       </c>
       <c r="B17" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>131106289</v>
       </c>
       <c r="B18" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>131106318</v>
       </c>
       <c r="B19" t="n">
-        <v>92114</v>
+        <v>92115</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2857,10 +2857,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131106310</v>
+        <v>131106313</v>
       </c>
       <c r="B20" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2885,17 +2885,26 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Grunnes gamla tomt, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>601470</v>
+        <v>601530</v>
       </c>
       <c r="R20" t="n">
-        <v>6992568</v>
+        <v>6992589</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2922,7 +2931,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2025_0874</t>
+          <t>2025_0871</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2932,7 +2941,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2942,7 +2951,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2962,7 +2971,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2973,10 +2982,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131106313</v>
+        <v>131106310</v>
       </c>
       <c r="B21" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3001,26 +3010,17 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Grunnes gamla tomt, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>601530</v>
+        <v>601470</v>
       </c>
       <c r="R21" t="n">
-        <v>6992589</v>
+        <v>6992568</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2025_0871</t>
+          <t>2025_0874</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -3101,7 +3101,7 @@
         <v>131106317</v>
       </c>
       <c r="B22" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3214,10 +3214,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131108353</v>
+        <v>131106327</v>
       </c>
       <c r="B23" t="n">
-        <v>10966</v>
+        <v>91817</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3225,26 +3225,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>101449</v>
+        <v>1202</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3253,10 +3254,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>601612</v>
+        <v>601607</v>
       </c>
       <c r="R23" t="n">
-        <v>6992796</v>
+        <v>6992789</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3283,7 +3284,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2025_0855</t>
+          <t>2025_0856</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -3293,7 +3294,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3303,12 +3304,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:09</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Granlåga med både rynkskinn, ull-och violticka</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3328,7 +3324,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>David Isaksson, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3342,7 +3338,7 @@
         <v>131106311</v>
       </c>
       <c r="B24" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3455,10 +3451,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131106327</v>
+        <v>131108353</v>
       </c>
       <c r="B25" t="n">
-        <v>91816</v>
+        <v>10966</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3466,27 +3462,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Paykull, 1790)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3495,10 +3490,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>601607</v>
+        <v>601612</v>
       </c>
       <c r="R25" t="n">
-        <v>6992789</v>
+        <v>6992796</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3525,7 +3520,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2025_0856</t>
+          <t>2025_0855</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -3535,7 +3530,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3545,7 +3540,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Granlåga med både rynkskinn, ull-och violticka</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>David Isaksson, Alexander Hoffmann</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3579,7 +3579,7 @@
         <v>131106323</v>
       </c>
       <c r="B26" t="n">
-        <v>92114</v>
+        <v>92115</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3692,45 +3692,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131106330</v>
+        <v>131106329</v>
       </c>
       <c r="B27" t="n">
-        <v>92114</v>
+        <v>92276</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Grunnes gamla tomt, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>601607</v>
+        <v>601609</v>
       </c>
       <c r="R27" t="n">
-        <v>6992782</v>
+        <v>6992789</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3757,7 +3762,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2025_0853</t>
+          <t>2025_0854</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3767,7 +3772,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3777,7 +3782,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3808,50 +3813,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131106329</v>
+        <v>131106330</v>
       </c>
       <c r="B28" t="n">
-        <v>92275</v>
+        <v>92115</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Grunnes gamla tomt, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>601609</v>
+        <v>601607</v>
       </c>
       <c r="R28" t="n">
-        <v>6992789</v>
+        <v>6992782</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2025_0854</t>
+          <t>2025_0853</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 62197-2025 artfynd.xlsx
+++ b/artfynd/A 62197-2025 artfynd.xlsx
@@ -1642,7 +1642,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131106319</v>
+        <v>131106315</v>
       </c>
       <c r="B10" t="n">
         <v>92115</v>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>601569</v>
+        <v>601573</v>
       </c>
       <c r="R10" t="n">
-        <v>6992657</v>
+        <v>6992600</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2025_0864</t>
+          <t>2025_0868</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1767,7 +1767,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131106315</v>
+        <v>131106319</v>
       </c>
       <c r="B11" t="n">
         <v>92115</v>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1811,10 +1811,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>601573</v>
+        <v>601569</v>
       </c>
       <c r="R11" t="n">
-        <v>6992600</v>
+        <v>6992657</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2025_0868</t>
+          <t>2025_0864</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -2013,7 +2013,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131106314</v>
+        <v>131106325</v>
       </c>
       <c r="B13" t="n">
         <v>91817</v>
@@ -2041,11 +2041,7 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>mycel</t>
@@ -2057,10 +2053,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601556</v>
+        <v>601615</v>
       </c>
       <c r="R13" t="n">
-        <v>6992605</v>
+        <v>6992785</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2087,7 +2083,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2025_0870</t>
+          <t>2025_0858</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2097,7 +2093,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2107,7 +2103,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2127,7 +2123,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2259,7 +2255,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131106325</v>
+        <v>131106314</v>
       </c>
       <c r="B15" t="n">
         <v>91817</v>
@@ -2287,7 +2283,11 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>mycel</t>
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>601615</v>
+        <v>601556</v>
       </c>
       <c r="R15" t="n">
-        <v>6992785</v>
+        <v>6992605</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2025_0858</t>
+          <t>2025_0870</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -3214,10 +3214,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131106327</v>
+        <v>131108353</v>
       </c>
       <c r="B23" t="n">
-        <v>91817</v>
+        <v>10966</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3225,27 +3225,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Paykull, 1790)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3254,10 +3253,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>601607</v>
+        <v>601612</v>
       </c>
       <c r="R23" t="n">
-        <v>6992789</v>
+        <v>6992796</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3284,7 +3283,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2025_0856</t>
+          <t>2025_0855</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -3294,7 +3293,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3304,7 +3303,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Granlåga med både rynkskinn, ull-och violticka</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3324,7 +3328,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>David Isaksson, Alexander Hoffmann</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3335,10 +3339,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131106311</v>
+        <v>131106323</v>
       </c>
       <c r="B24" t="n">
-        <v>91817</v>
+        <v>92115</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3346,21 +3350,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3370,10 +3374,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>601498</v>
+        <v>601607</v>
       </c>
       <c r="R24" t="n">
-        <v>6992583</v>
+        <v>6992738</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3400,7 +3404,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2025_0873</t>
+          <t>2025_0860</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -3410,7 +3414,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3420,7 +3424,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3440,7 +3444,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3451,10 +3455,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131108353</v>
+        <v>131106327</v>
       </c>
       <c r="B25" t="n">
-        <v>10966</v>
+        <v>91817</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3462,26 +3466,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>101449</v>
+        <v>1202</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3490,10 +3495,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>601612</v>
+        <v>601607</v>
       </c>
       <c r="R25" t="n">
-        <v>6992796</v>
+        <v>6992789</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3520,7 +3525,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2025_0855</t>
+          <t>2025_0856</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -3530,7 +3535,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3540,12 +3545,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:09</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Granlåga med både rynkskinn, ull-och violticka</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>David Isaksson, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3576,10 +3576,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131106323</v>
+        <v>131106311</v>
       </c>
       <c r="B26" t="n">
-        <v>92115</v>
+        <v>91817</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3587,21 +3587,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3611,10 +3611,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>601607</v>
+        <v>601498</v>
       </c>
       <c r="R26" t="n">
-        <v>6992738</v>
+        <v>6992583</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2025_0860</t>
+          <t>2025_0873</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">

--- a/artfynd/A 62197-2025 artfynd.xlsx
+++ b/artfynd/A 62197-2025 artfynd.xlsx
@@ -1642,39 +1642,35 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131106315</v>
+        <v>131106321</v>
       </c>
       <c r="B10" t="n">
-        <v>92115</v>
+        <v>92030</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>mycel</t>
@@ -1686,10 +1682,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>601573</v>
+        <v>601579</v>
       </c>
       <c r="R10" t="n">
-        <v>6992600</v>
+        <v>6992698</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1716,7 +1712,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2025_0868</t>
+          <t>2025_0862</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1726,7 +1722,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1736,7 +1732,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1756,7 +1752,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1892,35 +1888,39 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131106321</v>
+        <v>131106315</v>
       </c>
       <c r="B12" t="n">
-        <v>92030</v>
+        <v>92115</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>48</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>mycel</t>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>601579</v>
+        <v>601573</v>
       </c>
       <c r="R12" t="n">
-        <v>6992698</v>
+        <v>6992600</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2025_0862</t>
+          <t>2025_0868</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2013,7 +2013,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131106325</v>
+        <v>131106314</v>
       </c>
       <c r="B13" t="n">
         <v>91817</v>
@@ -2041,7 +2041,11 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>mycel</t>
@@ -2053,10 +2057,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601615</v>
+        <v>601556</v>
       </c>
       <c r="R13" t="n">
-        <v>6992785</v>
+        <v>6992605</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2083,7 +2087,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2025_0858</t>
+          <t>2025_0870</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2093,7 +2097,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2103,7 +2107,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2123,7 +2127,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2255,7 +2259,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131106314</v>
+        <v>131106325</v>
       </c>
       <c r="B15" t="n">
         <v>91817</v>
@@ -2283,11 +2287,7 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>mycel</t>
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>601556</v>
+        <v>601615</v>
       </c>
       <c r="R15" t="n">
-        <v>6992605</v>
+        <v>6992785</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2025_0870</t>
+          <t>2025_0858</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -3339,10 +3339,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131106323</v>
+        <v>131106327</v>
       </c>
       <c r="B24" t="n">
-        <v>92115</v>
+        <v>91817</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3350,24 +3350,29 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Grunnes gamla tomt, Ång</t>
@@ -3377,7 +3382,7 @@
         <v>601607</v>
       </c>
       <c r="R24" t="n">
-        <v>6992738</v>
+        <v>6992789</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3404,7 +3409,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2025_0860</t>
+          <t>2025_0856</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -3414,7 +3419,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3424,7 +3429,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3444,7 +3449,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>David Isaksson, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3455,10 +3460,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131106327</v>
+        <v>131106323</v>
       </c>
       <c r="B25" t="n">
-        <v>91817</v>
+        <v>92115</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3466,29 +3471,24 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Grunnes gamla tomt, Ång</t>
@@ -3498,7 +3498,7 @@
         <v>601607</v>
       </c>
       <c r="R25" t="n">
-        <v>6992789</v>
+        <v>6992738</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2025_0856</t>
+          <t>2025_0860</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>David Isaksson, Alexander Hoffmann</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3692,50 +3692,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131106329</v>
+        <v>131106330</v>
       </c>
       <c r="B27" t="n">
-        <v>92276</v>
+        <v>92115</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Grunnes gamla tomt, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>601609</v>
+        <v>601607</v>
       </c>
       <c r="R27" t="n">
-        <v>6992789</v>
+        <v>6992782</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3762,7 +3757,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2025_0854</t>
+          <t>2025_0853</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3772,7 +3767,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3782,7 +3777,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3813,45 +3808,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131106330</v>
+        <v>131106329</v>
       </c>
       <c r="B28" t="n">
-        <v>92115</v>
+        <v>92276</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Grunnes gamla tomt, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>601607</v>
+        <v>601609</v>
       </c>
       <c r="R28" t="n">
-        <v>6992782</v>
+        <v>6992789</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2025_0853</t>
+          <t>2025_0854</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 62197-2025 artfynd.xlsx
+++ b/artfynd/A 62197-2025 artfynd.xlsx
@@ -1055,7 +1055,7 @@
         <v>131106322</v>
       </c>
       <c r="B5" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>131106324</v>
       </c>
       <c r="B6" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>131106316</v>
       </c>
       <c r="B7" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>131106309</v>
       </c>
       <c r="B8" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>131106326</v>
       </c>
       <c r="B9" t="n">
-        <v>92188</v>
+        <v>92189</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>David Isaksson, Alexander Hoffmann, Anders Forsberg</t>
+          <t>Anders Forsberg, Alexander Hoffmann, David Isaksson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1642,35 +1642,39 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131106321</v>
+        <v>131106319</v>
       </c>
       <c r="B10" t="n">
-        <v>92030</v>
+        <v>92116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>48</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>mycel</t>
@@ -1682,10 +1686,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>601579</v>
+        <v>601569</v>
       </c>
       <c r="R10" t="n">
-        <v>6992698</v>
+        <v>6992657</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1712,7 +1716,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2025_0862</t>
+          <t>2025_0864</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1722,7 +1726,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1732,7 +1736,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1763,10 +1767,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131106319</v>
+        <v>131106315</v>
       </c>
       <c r="B11" t="n">
-        <v>92115</v>
+        <v>92116</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1797,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1807,10 +1811,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>601569</v>
+        <v>601573</v>
       </c>
       <c r="R11" t="n">
-        <v>6992657</v>
+        <v>6992600</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1837,7 +1841,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2025_0864</t>
+          <t>2025_0868</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1847,7 +1851,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1857,7 +1861,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1877,7 +1881,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1888,39 +1892,35 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131106315</v>
+        <v>131106321</v>
       </c>
       <c r="B12" t="n">
-        <v>92115</v>
+        <v>92031</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>mycel</t>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>601573</v>
+        <v>601579</v>
       </c>
       <c r="R12" t="n">
-        <v>6992600</v>
+        <v>6992698</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2025_0868</t>
+          <t>2025_0862</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2016,7 +2016,7 @@
         <v>131106314</v>
       </c>
       <c r="B13" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>131106312</v>
       </c>
       <c r="B14" t="n">
-        <v>92115</v>
+        <v>92116</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>131106325</v>
       </c>
       <c r="B15" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>131106308</v>
       </c>
       <c r="B16" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>131106320</v>
       </c>
       <c r="B17" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>131106289</v>
       </c>
       <c r="B18" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg, Jennifer Lehikoinen</t>
+          <t>Jennifer Lehikoinen, Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2735,7 +2735,7 @@
         <v>131106318</v>
       </c>
       <c r="B19" t="n">
-        <v>92115</v>
+        <v>92116</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2857,10 +2857,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131106313</v>
+        <v>131106310</v>
       </c>
       <c r="B20" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2885,26 +2885,17 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Grunnes gamla tomt, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>601530</v>
+        <v>601470</v>
       </c>
       <c r="R20" t="n">
-        <v>6992589</v>
+        <v>6992568</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2931,7 +2922,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2025_0871</t>
+          <t>2025_0874</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2941,7 +2932,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2951,7 +2942,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2971,7 +2962,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2982,10 +2973,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131106310</v>
+        <v>131106313</v>
       </c>
       <c r="B21" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3010,17 +3001,26 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Grunnes gamla tomt, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>601470</v>
+        <v>601530</v>
       </c>
       <c r="R21" t="n">
-        <v>6992568</v>
+        <v>6992589</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2025_0874</t>
+          <t>2025_0871</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -3101,7 +3101,7 @@
         <v>131106317</v>
       </c>
       <c r="B22" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3214,10 +3214,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131108353</v>
+        <v>131106311</v>
       </c>
       <c r="B23" t="n">
-        <v>10966</v>
+        <v>91818</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3225,38 +3225,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>101449</v>
+        <v>1202</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Grunnes gamla tomt, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>601612</v>
+        <v>601498</v>
       </c>
       <c r="R23" t="n">
-        <v>6992796</v>
+        <v>6992583</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3283,7 +3279,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2025_0855</t>
+          <t>2025_0873</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -3293,7 +3289,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3303,12 +3299,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:09</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Granlåga med både rynkskinn, ull-och violticka</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3328,7 +3319,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3342,7 +3333,7 @@
         <v>131106327</v>
       </c>
       <c r="B24" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3449,7 +3440,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>David Isaksson, Alexander Hoffmann</t>
+          <t>Alexander Hoffmann, David Isaksson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3463,7 +3454,7 @@
         <v>131106323</v>
       </c>
       <c r="B25" t="n">
-        <v>92115</v>
+        <v>92116</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3576,10 +3567,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131106311</v>
+        <v>131108353</v>
       </c>
       <c r="B26" t="n">
-        <v>91817</v>
+        <v>10966</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3587,34 +3578,38 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Paykull, 1790)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Grunnes gamla tomt, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>601498</v>
+        <v>601612</v>
       </c>
       <c r="R26" t="n">
-        <v>6992583</v>
+        <v>6992796</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3641,7 +3636,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2025_0873</t>
+          <t>2025_0855</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3651,7 +3646,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3661,7 +3656,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Granlåga med både rynkskinn, ull-och violticka</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3695,7 +3695,7 @@
         <v>131106330</v>
       </c>
       <c r="B27" t="n">
-        <v>92115</v>
+        <v>92116</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>David Isaksson, Alexander Hoffmann</t>
+          <t>Alexander Hoffmann, David Isaksson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3811,7 +3811,7 @@
         <v>131106329</v>
       </c>
       <c r="B28" t="n">
-        <v>92276</v>
+        <v>92277</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>David Isaksson, Alexander Hoffmann</t>
+          <t>Alexander Hoffmann, David Isaksson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">

--- a/artfynd/A 62197-2025 artfynd.xlsx
+++ b/artfynd/A 62197-2025 artfynd.xlsx
@@ -1631,7 +1631,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Forsberg, Alexander Hoffmann, David Isaksson</t>
+          <t>David Isaksson, Alexander Hoffmann, Anders Forsberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jennifer Lehikoinen, Linnéa Kjellberg</t>
+          <t>Linnéa Kjellberg, Jennifer Lehikoinen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, David Isaksson</t>
+          <t>David Isaksson, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3692,45 +3692,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131106330</v>
+        <v>131106329</v>
       </c>
       <c r="B27" t="n">
-        <v>92116</v>
+        <v>92277</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Grunnes gamla tomt, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>601607</v>
+        <v>601609</v>
       </c>
       <c r="R27" t="n">
-        <v>6992782</v>
+        <v>6992789</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3757,7 +3762,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2025_0853</t>
+          <t>2025_0854</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3767,7 +3772,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3777,7 +3782,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3797,7 +3802,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, David Isaksson</t>
+          <t>David Isaksson, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3808,50 +3813,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131106329</v>
+        <v>131106330</v>
       </c>
       <c r="B28" t="n">
-        <v>92277</v>
+        <v>92116</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Grunnes gamla tomt, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>601609</v>
+        <v>601607</v>
       </c>
       <c r="R28" t="n">
-        <v>6992789</v>
+        <v>6992782</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2025_0854</t>
+          <t>2025_0853</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, David Isaksson</t>
+          <t>David Isaksson, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">

--- a/artfynd/A 62197-2025 artfynd.xlsx
+++ b/artfynd/A 62197-2025 artfynd.xlsx
@@ -2013,10 +2013,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131106314</v>
+        <v>131106312</v>
       </c>
       <c r="B13" t="n">
-        <v>91818</v>
+        <v>92116</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2024,28 +2024,24 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>mycel</t>
@@ -2057,10 +2053,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601556</v>
+        <v>601540</v>
       </c>
       <c r="R13" t="n">
-        <v>6992605</v>
+        <v>6992576</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2087,7 +2083,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2025_0870</t>
+          <t>2025_0872</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2097,7 +2093,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2107,7 +2103,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2127,7 +2123,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2138,10 +2134,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131106312</v>
+        <v>131106325</v>
       </c>
       <c r="B14" t="n">
-        <v>92116</v>
+        <v>91818</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,21 +2145,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2178,10 +2174,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601540</v>
+        <v>601615</v>
       </c>
       <c r="R14" t="n">
-        <v>6992576</v>
+        <v>6992785</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2208,7 +2204,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2025_0872</t>
+          <t>2025_0858</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2218,7 +2214,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2228,7 +2224,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2259,7 +2255,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131106325</v>
+        <v>131106314</v>
       </c>
       <c r="B15" t="n">
         <v>91818</v>
@@ -2287,7 +2283,11 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>mycel</t>
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>601615</v>
+        <v>601556</v>
       </c>
       <c r="R15" t="n">
-        <v>6992785</v>
+        <v>6992605</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2025_0858</t>
+          <t>2025_0870</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">

--- a/artfynd/A 62197-2025 artfynd.xlsx
+++ b/artfynd/A 62197-2025 artfynd.xlsx
@@ -1055,7 +1055,7 @@
         <v>131106322</v>
       </c>
       <c r="B5" t="n">
-        <v>91818</v>
+        <v>91821</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>131106324</v>
       </c>
       <c r="B6" t="n">
-        <v>91818</v>
+        <v>91821</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>131106316</v>
       </c>
       <c r="B7" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>131106309</v>
       </c>
       <c r="B8" t="n">
-        <v>91818</v>
+        <v>91821</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>131106326</v>
       </c>
       <c r="B9" t="n">
-        <v>92189</v>
+        <v>92192</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>131106319</v>
       </c>
       <c r="B10" t="n">
-        <v>92116</v>
+        <v>92119</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>131106315</v>
       </c>
       <c r="B11" t="n">
-        <v>92116</v>
+        <v>92119</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>131106321</v>
       </c>
       <c r="B12" t="n">
-        <v>92031</v>
+        <v>92034</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2013,10 +2013,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131106312</v>
+        <v>131106314</v>
       </c>
       <c r="B13" t="n">
-        <v>92116</v>
+        <v>91821</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2024,24 +2024,28 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>mycel</t>
@@ -2053,10 +2057,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601540</v>
+        <v>601556</v>
       </c>
       <c r="R13" t="n">
-        <v>6992576</v>
+        <v>6992605</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2083,7 +2087,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2025_0872</t>
+          <t>2025_0870</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2093,7 +2097,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2103,7 +2107,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2123,7 +2127,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2134,10 +2138,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131106325</v>
+        <v>131106312</v>
       </c>
       <c r="B14" t="n">
-        <v>91818</v>
+        <v>92119</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2145,21 +2149,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2174,10 +2178,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601615</v>
+        <v>601540</v>
       </c>
       <c r="R14" t="n">
-        <v>6992785</v>
+        <v>6992576</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2204,7 +2208,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2025_0858</t>
+          <t>2025_0872</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2214,7 +2218,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2224,7 +2228,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2255,10 +2259,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131106314</v>
+        <v>131106325</v>
       </c>
       <c r="B15" t="n">
-        <v>91818</v>
+        <v>91821</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2283,11 +2287,7 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>mycel</t>
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>601556</v>
+        <v>601615</v>
       </c>
       <c r="R15" t="n">
-        <v>6992605</v>
+        <v>6992785</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2025_0870</t>
+          <t>2025_0858</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2383,7 +2383,7 @@
         <v>131106308</v>
       </c>
       <c r="B16" t="n">
-        <v>91818</v>
+        <v>91821</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>131106320</v>
       </c>
       <c r="B17" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>131106289</v>
       </c>
       <c r="B18" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>131106318</v>
       </c>
       <c r="B19" t="n">
-        <v>92116</v>
+        <v>92119</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>131106310</v>
       </c>
       <c r="B20" t="n">
-        <v>91818</v>
+        <v>91821</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>131106313</v>
       </c>
       <c r="B21" t="n">
-        <v>91818</v>
+        <v>91821</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         <v>131106317</v>
       </c>
       <c r="B22" t="n">
-        <v>91818</v>
+        <v>91821</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>131106311</v>
       </c>
       <c r="B23" t="n">
-        <v>91818</v>
+        <v>91821</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>131106327</v>
       </c>
       <c r="B24" t="n">
-        <v>91818</v>
+        <v>91821</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>131106323</v>
       </c>
       <c r="B25" t="n">
-        <v>92116</v>
+        <v>92119</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         <v>131108353</v>
       </c>
       <c r="B26" t="n">
-        <v>10966</v>
+        <v>10968</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3692,50 +3692,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131106329</v>
+        <v>131106330</v>
       </c>
       <c r="B27" t="n">
-        <v>92277</v>
+        <v>92119</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Grunnes gamla tomt, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>601609</v>
+        <v>601607</v>
       </c>
       <c r="R27" t="n">
-        <v>6992789</v>
+        <v>6992782</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3762,7 +3757,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2025_0854</t>
+          <t>2025_0853</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3772,7 +3767,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3782,7 +3777,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3813,45 +3808,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131106330</v>
+        <v>131106329</v>
       </c>
       <c r="B28" t="n">
-        <v>92116</v>
+        <v>92280</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Grunnes gamla tomt, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>601607</v>
+        <v>601609</v>
       </c>
       <c r="R28" t="n">
-        <v>6992782</v>
+        <v>6992789</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2025_0853</t>
+          <t>2025_0854</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 62197-2025 artfynd.xlsx
+++ b/artfynd/A 62197-2025 artfynd.xlsx
@@ -1055,7 +1055,7 @@
         <v>131106322</v>
       </c>
       <c r="B5" t="n">
-        <v>91821</v>
+        <v>91822</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>131106324</v>
       </c>
       <c r="B6" t="n">
-        <v>91821</v>
+        <v>91822</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>131106316</v>
       </c>
       <c r="B7" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>131106309</v>
       </c>
       <c r="B8" t="n">
-        <v>91821</v>
+        <v>91822</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>131106326</v>
       </c>
       <c r="B9" t="n">
-        <v>92192</v>
+        <v>92193</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1642,10 +1642,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131106319</v>
+        <v>131106315</v>
       </c>
       <c r="B10" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>601569</v>
+        <v>601573</v>
       </c>
       <c r="R10" t="n">
-        <v>6992657</v>
+        <v>6992600</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2025_0864</t>
+          <t>2025_0868</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1767,10 +1767,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131106315</v>
+        <v>131106319</v>
       </c>
       <c r="B11" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1811,10 +1811,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>601573</v>
+        <v>601569</v>
       </c>
       <c r="R11" t="n">
-        <v>6992600</v>
+        <v>6992657</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2025_0868</t>
+          <t>2025_0864</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1895,7 +1895,7 @@
         <v>131106321</v>
       </c>
       <c r="B12" t="n">
-        <v>92034</v>
+        <v>92035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2013,10 +2013,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131106314</v>
+        <v>131106325</v>
       </c>
       <c r="B13" t="n">
-        <v>91821</v>
+        <v>91822</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2041,11 +2041,7 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>mycel</t>
@@ -2057,10 +2053,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601556</v>
+        <v>601615</v>
       </c>
       <c r="R13" t="n">
-        <v>6992605</v>
+        <v>6992785</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2087,7 +2083,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2025_0870</t>
+          <t>2025_0858</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2097,7 +2093,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2107,7 +2103,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2127,7 +2123,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2141,7 +2137,7 @@
         <v>131106312</v>
       </c>
       <c r="B14" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2259,10 +2255,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131106325</v>
+        <v>131106314</v>
       </c>
       <c r="B15" t="n">
-        <v>91821</v>
+        <v>91822</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2287,7 +2283,11 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>mycel</t>
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>601615</v>
+        <v>601556</v>
       </c>
       <c r="R15" t="n">
-        <v>6992785</v>
+        <v>6992605</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2025_0858</t>
+          <t>2025_0870</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2383,7 +2383,7 @@
         <v>131106308</v>
       </c>
       <c r="B16" t="n">
-        <v>91821</v>
+        <v>91822</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>131106320</v>
       </c>
       <c r="B17" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>131106289</v>
       </c>
       <c r="B18" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>131106318</v>
       </c>
       <c r="B19" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2857,10 +2857,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131106310</v>
+        <v>131106313</v>
       </c>
       <c r="B20" t="n">
-        <v>91821</v>
+        <v>91822</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2885,17 +2885,26 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Grunnes gamla tomt, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>601470</v>
+        <v>601530</v>
       </c>
       <c r="R20" t="n">
-        <v>6992568</v>
+        <v>6992589</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2922,7 +2931,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2025_0874</t>
+          <t>2025_0871</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2932,7 +2941,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2942,7 +2951,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2962,7 +2971,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2973,10 +2982,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131106313</v>
+        <v>131106310</v>
       </c>
       <c r="B21" t="n">
-        <v>91821</v>
+        <v>91822</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3001,26 +3010,17 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Grunnes gamla tomt, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>601530</v>
+        <v>601470</v>
       </c>
       <c r="R21" t="n">
-        <v>6992589</v>
+        <v>6992568</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2025_0871</t>
+          <t>2025_0874</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -3101,7 +3101,7 @@
         <v>131106317</v>
       </c>
       <c r="B22" t="n">
-        <v>91821</v>
+        <v>91822</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3214,10 +3214,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131106311</v>
+        <v>131106323</v>
       </c>
       <c r="B23" t="n">
-        <v>91821</v>
+        <v>92120</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3225,21 +3225,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>601498</v>
+        <v>601607</v>
       </c>
       <c r="R23" t="n">
-        <v>6992583</v>
+        <v>6992738</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2025_0873</t>
+          <t>2025_0860</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3333,7 +3333,7 @@
         <v>131106327</v>
       </c>
       <c r="B24" t="n">
-        <v>91821</v>
+        <v>91822</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3451,10 +3451,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131106323</v>
+        <v>131106311</v>
       </c>
       <c r="B25" t="n">
-        <v>92119</v>
+        <v>91822</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3462,21 +3462,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3486,10 +3486,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>601607</v>
+        <v>601498</v>
       </c>
       <c r="R25" t="n">
-        <v>6992738</v>
+        <v>6992583</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2025_0860</t>
+          <t>2025_0873</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3692,45 +3692,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131106330</v>
+        <v>131106329</v>
       </c>
       <c r="B27" t="n">
-        <v>92119</v>
+        <v>92281</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Grunnes gamla tomt, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>601607</v>
+        <v>601609</v>
       </c>
       <c r="R27" t="n">
-        <v>6992782</v>
+        <v>6992789</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3757,7 +3762,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2025_0853</t>
+          <t>2025_0854</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3767,7 +3772,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3777,7 +3782,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3808,50 +3813,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131106329</v>
+        <v>131106330</v>
       </c>
       <c r="B28" t="n">
-        <v>92280</v>
+        <v>92120</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Grunnes gamla tomt, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>601609</v>
+        <v>601607</v>
       </c>
       <c r="R28" t="n">
-        <v>6992789</v>
+        <v>6992782</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2025_0854</t>
+          <t>2025_0853</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 62197-2025 artfynd.xlsx
+++ b/artfynd/A 62197-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,59 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123299589</v>
+        <v>131106321</v>
       </c>
       <c r="B2" t="n">
-        <v>96963</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92123</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>48</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Romell) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Brännan, Ång</t>
+          <t>Grunnes gamla tomt, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601495</v>
+        <v>601579</v>
       </c>
       <c r="R2" t="n">
-        <v>6992480</v>
+        <v>6992698</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,32 +745,27 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>2025_0862</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>07:27</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>07:27</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>enstaka bestånd i ung produktionsskog</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +785,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elsa Fogelström</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -810,15 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123299587</v>
+        <v>131106312</v>
       </c>
       <c r="B3" t="n">
-        <v>91008</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -826,34 +807,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Brännan, Ång</t>
+          <t>Grunnes gamla tomt, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601491</v>
+        <v>601540</v>
       </c>
       <c r="R3" t="n">
-        <v>6992567</v>
+        <v>6992576</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,27 +866,27 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>2025_0872</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:39</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:39</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -931,15 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123299588</v>
+        <v>131106315</v>
       </c>
       <c r="B4" t="n">
-        <v>90990</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,34 +928,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Brännan, Ång</t>
+          <t>Grunnes gamla tomt, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601482</v>
+        <v>601573</v>
       </c>
       <c r="R4" t="n">
-        <v>6992515</v>
+        <v>6992600</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,27 +991,27 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>2025_0868</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,7 +1031,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1052,10 +1042,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131106322</v>
+        <v>131106318</v>
       </c>
       <c r="B5" t="n">
-        <v>91822</v>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,24 +1053,28 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>mycel</t>
@@ -1092,10 +1086,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601612</v>
+        <v>601572</v>
       </c>
       <c r="R5" t="n">
-        <v>6992728</v>
+        <v>6992627</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,7 +1116,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2025_0861</t>
+          <t>2025_0865</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1132,7 +1126,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1142,7 +1136,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1162,7 +1156,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1173,10 +1167,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131106324</v>
+        <v>131106319</v>
       </c>
       <c r="B6" t="n">
-        <v>91822</v>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,34 +1178,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Grunnes gamla tomt, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601605</v>
+        <v>601569</v>
       </c>
       <c r="R6" t="n">
-        <v>6992737</v>
+        <v>6992657</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1238,7 +1241,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2025_0859</t>
+          <t>2025_0864</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1248,7 +1251,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1258,7 +1261,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,7 +1281,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1289,10 +1292,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131106316</v>
+        <v>131106323</v>
       </c>
       <c r="B7" t="n">
-        <v>79254</v>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,21 +1303,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1324,10 +1327,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601561</v>
+        <v>601607</v>
       </c>
       <c r="R7" t="n">
-        <v>6992629</v>
+        <v>6992738</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1354,7 +1357,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2025_0867</t>
+          <t>2025_0860</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1364,7 +1367,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1374,7 +1377,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1394,7 +1397,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1405,10 +1408,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131106309</v>
+        <v>131106330</v>
       </c>
       <c r="B8" t="n">
-        <v>91822</v>
+        <v>92208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,21 +1419,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1440,10 +1443,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601504</v>
+        <v>601607</v>
       </c>
       <c r="R8" t="n">
-        <v>6992544</v>
+        <v>6992782</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1470,7 +1473,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2025_0875</t>
+          <t>2025_0853</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1480,7 +1483,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1490,7 +1493,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1510,7 +1513,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>David Isaksson, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1521,50 +1524,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131106326</v>
+        <v>123299588</v>
       </c>
       <c r="B9" t="n">
-        <v>92193</v>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Grunnes gamla tomt, Ång</t>
+          <t>Brännan, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601617</v>
+        <v>601482</v>
       </c>
       <c r="R9" t="n">
-        <v>6992789</v>
+        <v>6992515</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1591,27 +1589,27 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2025_0857</t>
+          <t>356</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1631,7 +1629,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>David Isaksson, Alexander Hoffmann, Anders Forsberg</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1642,10 +1640,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131106315</v>
+        <v>131106308</v>
       </c>
       <c r="B10" t="n">
-        <v>92120</v>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1653,43 +1651,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Grunnes gamla tomt, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>601573</v>
+        <v>601505</v>
       </c>
       <c r="R10" t="n">
-        <v>6992600</v>
+        <v>6992571</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1716,7 +1705,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2025_0868</t>
+          <t>2025_0876</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1726,7 +1715,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1736,7 +1725,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1756,7 +1745,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1767,10 +1756,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131106319</v>
+        <v>131106309</v>
       </c>
       <c r="B11" t="n">
-        <v>92120</v>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1778,43 +1767,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Grunnes gamla tomt, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>601569</v>
+        <v>601504</v>
       </c>
       <c r="R11" t="n">
-        <v>6992657</v>
+        <v>6992544</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1841,7 +1821,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2025_0864</t>
+          <t>2025_0875</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1851,7 +1831,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1861,7 +1841,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1892,50 +1872,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131106321</v>
+        <v>131106310</v>
       </c>
       <c r="B12" t="n">
-        <v>92035</v>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>48</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Grunnes gamla tomt, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>601579</v>
+        <v>601470</v>
       </c>
       <c r="R12" t="n">
-        <v>6992698</v>
+        <v>6992568</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1962,7 +1937,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2025_0862</t>
+          <t>2025_0874</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1972,7 +1947,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1982,7 +1957,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2013,10 +1988,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131106325</v>
+        <v>131106311</v>
       </c>
       <c r="B13" t="n">
-        <v>91822</v>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2042,21 +2017,16 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Grunnes gamla tomt, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601615</v>
+        <v>601498</v>
       </c>
       <c r="R13" t="n">
-        <v>6992785</v>
+        <v>6992583</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2083,7 +2053,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2025_0858</t>
+          <t>2025_0873</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2093,7 +2063,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2103,7 +2073,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2134,10 +2104,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131106312</v>
+        <v>131106313</v>
       </c>
       <c r="B14" t="n">
-        <v>92120</v>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2145,24 +2115,28 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>mycel</t>
@@ -2174,10 +2148,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601540</v>
+        <v>601530</v>
       </c>
       <c r="R14" t="n">
-        <v>6992576</v>
+        <v>6992589</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2204,7 +2178,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2025_0872</t>
+          <t>2025_0871</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2244,7 +2218,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2258,7 +2232,7 @@
         <v>131106314</v>
       </c>
       <c r="B15" t="n">
-        <v>91822</v>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2380,10 +2354,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131106308</v>
+        <v>131106317</v>
       </c>
       <c r="B16" t="n">
-        <v>91822</v>
+        <v>91909</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2415,10 +2389,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>601505</v>
+        <v>601567</v>
       </c>
       <c r="R16" t="n">
-        <v>6992571</v>
+        <v>6992627</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2445,7 +2419,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2025_0876</t>
+          <t>2025_0866</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2455,7 +2429,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2465,7 +2439,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2496,10 +2470,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131106320</v>
+        <v>131106322</v>
       </c>
       <c r="B17" t="n">
-        <v>58051</v>
+        <v>91909</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2507,34 +2481,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gunnes gamla tomt, Ång</t>
+          <t>Grunnes gamla tomt, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>601577</v>
+        <v>601612</v>
       </c>
       <c r="R17" t="n">
-        <v>6992687</v>
+        <v>6992728</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2561,7 +2540,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2025_0863</t>
+          <t>2025_0861</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2571,7 +2550,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2581,7 +2560,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2601,7 +2580,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Forsberg</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2612,10 +2591,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131106289</v>
+        <v>131106324</v>
       </c>
       <c r="B18" t="n">
-        <v>58051</v>
+        <v>91909</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2623,38 +2602,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Håviksmyran, Ång</t>
+          <t>Grunnes gamla tomt, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>601411</v>
+        <v>601605</v>
       </c>
       <c r="R18" t="n">
-        <v>6992338</v>
+        <v>6992737</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2681,27 +2656,27 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2025_0895</t>
+          <t>2025_0859</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2721,7 +2696,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg, Jennifer Lehikoinen</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2732,10 +2707,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131106318</v>
+        <v>131106325</v>
       </c>
       <c r="B19" t="n">
-        <v>92120</v>
+        <v>91909</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2743,28 +2718,24 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>mycel</t>
@@ -2776,10 +2747,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>601572</v>
+        <v>601615</v>
       </c>
       <c r="R19" t="n">
-        <v>6992627</v>
+        <v>6992785</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2806,7 +2777,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2025_0865</t>
+          <t>2025_0858</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2816,7 +2787,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2826,7 +2797,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2846,7 +2817,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2857,10 +2828,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131106313</v>
+        <v>131106327</v>
       </c>
       <c r="B20" t="n">
-        <v>91822</v>
+        <v>91909</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2885,11 +2856,7 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>mycel</t>
@@ -2901,10 +2868,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>601530</v>
+        <v>601607</v>
       </c>
       <c r="R20" t="n">
-        <v>6992589</v>
+        <v>6992789</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2931,7 +2898,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2025_0871</t>
+          <t>2025_0856</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2941,7 +2908,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2951,7 +2918,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2971,7 +2938,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>David Isaksson, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2982,10 +2949,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131106310</v>
+        <v>131106329</v>
       </c>
       <c r="B21" t="n">
-        <v>91822</v>
+        <v>92369</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2993,34 +2960,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Grunnes gamla tomt, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>601470</v>
+        <v>601609</v>
       </c>
       <c r="R21" t="n">
-        <v>6992568</v>
+        <v>6992789</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3047,7 +3019,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2025_0874</t>
+          <t>2025_0854</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -3057,7 +3029,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3067,7 +3039,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3087,7 +3059,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>David Isaksson, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -3098,45 +3070,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131106317</v>
+        <v>131106326</v>
       </c>
       <c r="B22" t="n">
-        <v>91822</v>
+        <v>92281</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Grunnes gamla tomt, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>601567</v>
+        <v>601617</v>
       </c>
       <c r="R22" t="n">
-        <v>6992627</v>
+        <v>6992789</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3163,7 +3140,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2025_0866</t>
+          <t>2025_0857</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -3173,7 +3150,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3183,7 +3160,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3203,7 +3180,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>David Isaksson, Alexander Hoffmann, Anders Forsberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3214,32 +3191,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131106323</v>
+        <v>131106316</v>
       </c>
       <c r="B23" t="n">
-        <v>92120</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3249,10 +3226,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>601607</v>
+        <v>601561</v>
       </c>
       <c r="R23" t="n">
-        <v>6992738</v>
+        <v>6992629</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3279,7 +3256,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2025_0860</t>
+          <t>2025_0867</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -3289,7 +3266,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3299,7 +3276,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3319,7 +3296,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3330,10 +3307,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131106327</v>
+        <v>131108353</v>
       </c>
       <c r="B24" t="n">
-        <v>91822</v>
+        <v>10970</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3341,27 +3318,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Paykull, 1790)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3370,10 +3346,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>601607</v>
+        <v>601612</v>
       </c>
       <c r="R24" t="n">
-        <v>6992789</v>
+        <v>6992796</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3400,7 +3376,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2025_0856</t>
+          <t>2025_0855</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -3410,7 +3386,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3420,7 +3396,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Granlåga med både rynkskinn, ull-och violticka</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3440,7 +3421,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>David Isaksson, Alexander Hoffmann</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3451,10 +3432,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131106311</v>
+        <v>131106289</v>
       </c>
       <c r="B25" t="n">
-        <v>91822</v>
+        <v>58114</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3462,34 +3443,38 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Grunnes gamla tomt, Ång</t>
+          <t>Håviksmyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>601498</v>
+        <v>601411</v>
       </c>
       <c r="R25" t="n">
-        <v>6992583</v>
+        <v>6992338</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3516,27 +3501,27 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2025_0873</t>
+          <t>2025_0895</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3556,7 +3541,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Linnéa Kjellberg, Jennifer Lehikoinen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3567,10 +3552,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131108353</v>
+        <v>131106320</v>
       </c>
       <c r="B26" t="n">
-        <v>10968</v>
+        <v>58114</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3578,38 +3563,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>101449</v>
+        <v>103021</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Grunnes gamla tomt, Ång</t>
+          <t>Gunnes gamla tomt, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>601612</v>
+        <v>601577</v>
       </c>
       <c r="R26" t="n">
-        <v>6992796</v>
+        <v>6992687</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3636,7 +3617,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2025_0855</t>
+          <t>2025_0863</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3646,7 +3627,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3656,12 +3637,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:09</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Granlåga med både rynkskinn, ull-och violticka</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3681,7 +3657,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Anders Forsberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3692,50 +3668,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131106329</v>
+        <v>123299589</v>
       </c>
       <c r="B27" t="n">
-        <v>92281</v>
+        <v>97989</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>221941</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Grunnes gamla tomt, Ång</t>
+          <t>Brännan, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>601609</v>
+        <v>601495</v>
       </c>
       <c r="R27" t="n">
-        <v>6992789</v>
+        <v>6992480</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3762,27 +3742,32 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2025_0854</t>
+          <t>355</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>07:27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>07:27</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>enstaka bestånd i ung produktionsskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3802,126 +3787,10 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>David Isaksson, Alexander Hoffmann</t>
+          <t>Elsa Fogelström</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
-        <is>
-          <t>Kustpaketet</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>131106330</v>
-      </c>
-      <c r="B28" t="n">
-        <v>92120</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>658</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Fomitopsis rosea</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Grunnes gamla tomt, Ång</t>
-        </is>
-      </c>
-      <c r="Q28" t="n">
-        <v>601607</v>
-      </c>
-      <c r="R28" t="n">
-        <v>6992782</v>
-      </c>
-      <c r="S28" t="n">
-        <v>10</v>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>Graninge</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>2025_0853</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AD28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="inlineStr"/>
-      <c r="AW28" t="inlineStr">
-        <is>
-          <t>David Isaksson</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>David Isaksson, Alexander Hoffmann</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
         </is>

--- a/artfynd/A 62197-2025 artfynd.xlsx
+++ b/artfynd/A 62197-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106321</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106312</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1039,6 +1054,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106315</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1164,6 +1184,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106318</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1289,6 +1314,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106319</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1405,6 +1435,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106323</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1521,6 +1556,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106330</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1637,6 +1677,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123299588</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1753,6 +1798,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106308</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1869,6 +1919,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106309</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1985,6 +2040,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106310</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2101,6 +2161,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106311</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2226,6 +2291,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106313</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2351,6 +2421,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106314</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2467,6 +2542,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106317</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2588,6 +2668,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106322</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2704,6 +2789,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106324</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2825,6 +2915,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106325</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2946,6 +3041,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106327</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3067,6 +3167,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106329</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3188,6 +3293,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106326</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3304,6 +3414,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106316</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3429,6 +3544,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131108353</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3549,6 +3669,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106289</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3665,6 +3790,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106320</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3795,8 +3925,41 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123299589</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>